--- a/G5Dot/G5Dot/BOM_G5Dot_REV_01.01_VARIANT_Mosaic-G5_P3H.xlsx
+++ b/G5Dot/G5Dot/BOM_G5Dot_REV_01.01_VARIANT_Mosaic-G5_P3H.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://septentrio-my.sharepoint.com/personal/laetitia_kazingufu-furaha_septentrio_com/Documents/Documents/GitHub/MosaicM2G5/G5Dot 2/G5Dot 2/G5Dot/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://septentrio-my.sharepoint.com/personal/laetitia_kazingufu-furaha_septentrio_com/Documents/Documents/GitHub/G5Dot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{90B0780A-790E-460F-90C4-BFBB9720EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B122309-B0A7-438C-A717-61CBE99E41DA}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{90B0780A-790E-460F-90C4-BFBB9720EE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4593ADE2-A124-4C28-B24B-754D1315A825}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -43,27 +43,15 @@
     <t>Project Title:</t>
   </si>
   <si>
-    <t>ANavS GmbH</t>
-  </si>
-  <si>
     <t>Project File Name:</t>
   </si>
   <si>
-    <t>Gotthardstraße 40</t>
-  </si>
-  <si>
     <t xml:space="preserve">Assembly Variant: </t>
   </si>
   <si>
-    <t>80686 Munich</t>
-  </si>
-  <si>
     <t>Report Date:</t>
   </si>
   <si>
-    <t>Germany</t>
-  </si>
-  <si>
     <t>12.06.2025</t>
   </si>
   <si>
@@ -209,6 +197,18 @@
   </si>
   <si>
     <t>Septentrio</t>
+  </si>
+  <si>
+    <t>Interleuvenlaan 15i</t>
+  </si>
+  <si>
+    <t>3001 Leuven</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Geenhill Campus</t>
   </si>
 </sst>
 </file>
@@ -432,23 +432,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>59531</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2136887</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101809</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>799818</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>85443</xdr:rowOff>
+      <xdr:colOff>1197428</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>127244</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6E2A328-2C81-44DB-8616-A901C6A9AC30}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67BADEB8-C1B9-93C1-5582-1FB1FC6F48ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -457,47 +457,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="12337256" y="119062"/>
-          <a:ext cx="740287" cy="737906"/>
+          <a:off x="14283530" y="292309"/>
+          <a:ext cx="1210469" cy="406435"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -800,55 +772,55 @@
         <v>1</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E4" s="6"/>
       <c r="I4" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7"/>
       <c r="I5" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E6" s="7"/>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="4"/>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="J7" s="4"/>
     </row>
@@ -866,202 +838,202 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E12" s="15">
         <v>1</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E13" s="15">
         <v>1</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E14" s="15">
         <v>6</v>
       </c>
       <c r="F14" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="I14" s="14" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="2:10" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E15" s="15">
         <v>3</v>
       </c>
       <c r="F15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>43</v>
-      </c>
       <c r="I15" s="14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E16" s="15">
         <v>2</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B17" s="11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E17" s="15">
         <v>1</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E18" s="15">
         <v>1</v>
